--- a/exports/study_2026-05-12/TMC_NBeltLineRd_BarnesBridgeRd_2026-05-12.xlsx
+++ b/exports/study_2026-05-12/TMC_NBeltLineRd_BarnesBridgeRd_2026-05-12.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15515</v>
+        <v>14695</v>
       </c>
     </row>
     <row r="6">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="D7" t="n">
         <v>407</v>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>870</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6697</v>
+        <v>6442</v>
       </c>
       <c r="C8" t="n">
-        <v>1398</v>
+        <v>756</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8103</v>
+        <v>7206</v>
       </c>
     </row>
     <row r="9">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5614</v>
+        <v>5766</v>
       </c>
       <c r="C9" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D9" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>6085</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="10">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C10" t="n">
         <v>63</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>457</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11">
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>12580</v>
+        <v>12458</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>1966</v>
+        <v>1282</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>15</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>15515</v>
+        <v>14695</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +651,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>raw events: 15515</t>
+          <t>raw events: 14695</t>
         </is>
       </c>
     </row>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="D3" t="n">
         <v>407</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>870</v>
+        <v>824</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6697</v>
+        <v>6442</v>
       </c>
       <c r="C4" t="n">
-        <v>1398</v>
+        <v>756</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>8103</v>
+        <v>7206</v>
       </c>
     </row>
     <row r="5">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5614</v>
+        <v>5766</v>
       </c>
       <c r="C5" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D5" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6085</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="6">
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C6" t="n">
         <v>63</v>
       </c>
       <c r="D6" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>457</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C3" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
@@ -956,10 +956,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
         <v>12</v>
@@ -968,19 +968,19 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>701</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C4" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1002,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>13</v>
@@ -1014,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>726</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="C5" t="n">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1072,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>18</v>
@@ -1084,19 +1084,19 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>777</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>20</v>
@@ -1148,13 +1148,13 @@
         <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>756</v>
+        <v>723</v>
       </c>
     </row>
     <row r="7">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1176,22 +1176,22 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>624</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>16</v>
@@ -1258,19 +1258,19 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>623</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1304,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
@@ -1316,19 +1316,19 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>627</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1350,22 +1350,22 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>602</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11">
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>16</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>443</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>9</v>
@@ -1490,19 +1490,19 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>452</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13">
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>16</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>449</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1582,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
@@ -1606,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>486</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15">
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>528</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G16" t="n">
         <v>4</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>11</v>
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>479</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17">
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C17" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G17" t="n">
         <v>5</v>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>17</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>484</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
         <v>15</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>506</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C19" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="G19" t="n">
         <v>6</v>
@@ -1884,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>16</v>
@@ -1896,19 +1896,19 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>757</v>
+        <v>732</v>
       </c>
     </row>
     <row r="20">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G20" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>21</v>
@@ -1954,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>722</v>
+        <v>699</v>
       </c>
     </row>
     <row r="21">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="C21" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G21" t="n">
         <v>12</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
         <v>17</v>
@@ -2012,19 +2012,19 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>828</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C22" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="G22" t="n">
         <v>7</v>
@@ -2070,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>791</v>
+        <v>764</v>
       </c>
     </row>
     <row r="23">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C23" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="C24" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G24" t="n">
         <v>7</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>17</v>
@@ -2186,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
         <v>2</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>781</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C25" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G25" t="n">
         <v>7</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
@@ -2244,19 +2244,19 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>852</v>
+        <v>823</v>
       </c>
     </row>
     <row r="26">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -2302,19 +2302,19 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>754</v>
+        <v>734</v>
       </c>
     </row>
     <row r="27">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>6697</v>
+        <v>6442</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1398</v>
+        <v>756</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>7</v>
@@ -2336,22 +2336,22 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>5614</v>
+        <v>5766</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>407</v>
@@ -2360,19 +2360,19 @@
         <v>14</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>63</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="Q27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>15515</v>
+        <v>14695</v>
       </c>
     </row>
   </sheetData>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>15515</v>
+        <v>14695</v>
       </c>
     </row>
     <row r="2">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15515</v>
+        <v>14695</v>
       </c>
     </row>
   </sheetData>
